--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.58919386015945</v>
+        <v>7.24574400227591</v>
       </c>
       <c r="D2" t="n">
-        <v>44.77732527576384</v>
+        <v>7.276315357311623</v>
       </c>
       <c r="E2" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F2" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.24325908682324</v>
+        <v>5.727029601608777</v>
       </c>
       <c r="D3" t="n">
-        <v>19.6820213733808</v>
+        <v>3.198328473174379</v>
       </c>
       <c r="E3" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F3" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.51809901046157</v>
+        <v>2.846691089200005</v>
       </c>
       <c r="D4" t="n">
-        <v>13.48028510287609</v>
+        <v>2.190546329217364</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F4" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.06388397080134</v>
+        <v>6.510381145255218</v>
       </c>
       <c r="D5" t="n">
-        <v>34.20937652715145</v>
+        <v>5.559023685662111</v>
       </c>
       <c r="E5" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F5" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.28321363207633</v>
+        <v>4.596022215212404</v>
       </c>
       <c r="D6" t="n">
-        <v>24.6359346475852</v>
+        <v>4.003339380232595</v>
       </c>
       <c r="E6" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F6" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.83910340906246</v>
+        <v>3.22385430397265</v>
       </c>
       <c r="D7" t="n">
-        <v>44.35739793919472</v>
+        <v>7.208077165119142</v>
       </c>
       <c r="E7" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F7" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.860022573334675</v>
+        <v>1.439753668166885</v>
       </c>
       <c r="D8" t="n">
-        <v>27.0044952404756</v>
+        <v>4.388230476577284</v>
       </c>
       <c r="E8" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F8" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.6018569079807</v>
+        <v>4.972801747546864</v>
       </c>
       <c r="D9" t="n">
-        <v>41.75807788254721</v>
+        <v>6.785687655913923</v>
       </c>
       <c r="E9" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F9" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>52.25604696534597</v>
+        <v>8.491607631868721</v>
       </c>
       <c r="D10" t="n">
-        <v>65.26956990478224</v>
+        <v>10.60630510952712</v>
       </c>
       <c r="E10" t="n">
-        <v>13.08243867763792</v>
+        <v>2.125896285116162</v>
       </c>
       <c r="F10" t="n">
-        <v>14.96209177597621</v>
+        <v>2.431339913596134</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
